--- a/think3d_repro/outputs/run3/vlmeval_runs/SPAgent_4B_px256k_pi3x_spatial/BLINK/SPAgent_4B_px256k_pi3x_spatial_BLINK.xlsx
+++ b/think3d_repro/outputs/run3/vlmeval_runs/SPAgent_4B_px256k_pi3x_spatial/BLINK/SPAgent_4B_px256k_pi3x_spatial_BLINK.xlsx
@@ -916,16 +916,9 @@
     <t>&lt;answer&gt;(A) left&lt;/answer&gt;</t>
   </si>
   <si>
-    <t>The unresolved geometric quantity is the **lateral displacement sign** of the camera’s orbit, specifically whether the camera is moving clockwise (left) or counter-clockwise (right) around the central object (the mug).
-To resolve this, we must analyze the relative positions of the objects in the two images:
-- In the first image, the can is to the left of the mug, and the cigarette pack is to the right.
-- In the second image, the can is still to the left of the mug, and the cigarette pack is still to the right.
-- This indicates that the camera has not rotated in a way that would cause the can to appear to the right of the mug (which would happen if the camera were moving clockwise — left). Instead, the can remains to the left, suggesting the camera is moving counter-clockwise — right.
-This is consistent with the Pi3X tool’s result, which confirmed the relative positions remain unchanged in the 90° azimuth view, reinforcing that the camera is orbiting counter-clockwise.
-We now verify the selected option (right) against the original images’ object identities:
-- The can and cigarette pack retain their relative positions (can left, cigarette pack right) across both frames.
-- No object has disappeared or been occluded — the depth ordering is preserved, and the lateral displacement sign is consistent with counter-clockwise (right) motion.
-Thus, the correct answer is:
+    <t>The 3D reconstruction confirms the relative positions of the cameras and objects. Cam1 corresponds to the first image (beginning of video), and Cam2 corresponds to the second image (end of video). The mug and can are positioned such that in Cam1, the mug is to the left of the can, and in Cam2, the mug is to the right of the can. This lateral displacement indicates the camera has moved counter-clockwise (right) around the scene.
+The modular heading sum is: Cam1 (0°) → Cam2 (90° clockwise) → Cam1 (0°) → Cam2 (90° clockwise). The net rotation is 180°, which is consistent with counter-clockwise movement (right).
+The mug is visible in both images, and its position relative to the can confirms the direction of movement. The camera motion is right (counter-clockwise).
 &lt;answer&gt;B&lt;/answer&gt;</t>
   </si>
   <si>
